--- a/artfynd/A 30513-2026 artfynd.xlsx
+++ b/artfynd/A 30513-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79749287</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79750122</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134664983</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135058972</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1214,6 +1239,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665030</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1330,6 +1360,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665031</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1446,6 +1481,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134850251</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1562,6 +1602,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134850252</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1678,6 +1723,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134850253</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1784,6 +1834,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135058973</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1890,6 +1945,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135058974</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2006,6 +2066,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665048</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2112,6 +2177,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135058971</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2218,8 +2288,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135058975</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30513-2026 artfynd.xlsx
+++ b/artfynd/A 30513-2026 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>135058972</v>
       </c>
       <c r="B5" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>135058973</v>
       </c>
       <c r="B11" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>135058974</v>
       </c>
       <c r="B12" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>135058971</v>
       </c>
       <c r="B14" t="n">
-        <v>106324</v>
+        <v>106379</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>135058975</v>
       </c>
       <c r="B15" t="n">
-        <v>106324</v>
+        <v>106379</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 30513-2026 artfynd.xlsx
+++ b/artfynd/A 30513-2026 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>135058972</v>
       </c>
       <c r="B5" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>135058973</v>
       </c>
       <c r="B11" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>135058974</v>
       </c>
       <c r="B12" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>135058971</v>
       </c>
       <c r="B14" t="n">
-        <v>106379</v>
+        <v>106406</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>135058975</v>
       </c>
       <c r="B15" t="n">
-        <v>106379</v>
+        <v>106406</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 30513-2026 artfynd.xlsx
+++ b/artfynd/A 30513-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134664983</v>
+        <v>136042742</v>
       </c>
       <c r="B4" t="n">
-        <v>91995</v>
+        <v>93353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,26 +905,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>802121</v>
+        <v>802364</v>
       </c>
       <c r="R4" t="n">
-        <v>7353580</v>
+        <v>7353164</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -963,22 +963,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1009,16 +1009,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134664983</t>
+          <t>https://artportalen.se/Sighting/136042742</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135058972</v>
+        <v>136042770</v>
       </c>
       <c r="B5" t="n">
-        <v>92064</v>
+        <v>93361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,26 +1026,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1054,13 +1054,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>802158</v>
+        <v>802377</v>
       </c>
       <c r="R5" t="n">
-        <v>7353566</v>
+        <v>7353172</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,12 +1084,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1120,38 +1130,38 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135058972</t>
+          <t>https://artportalen.se/Sighting/136042770</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134665030</v>
+        <v>136042876</v>
       </c>
       <c r="B6" t="n">
-        <v>99195</v>
+        <v>93361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1165,13 +1175,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>802203</v>
+        <v>802276</v>
       </c>
       <c r="R6" t="n">
-        <v>7353559</v>
+        <v>7353275</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1195,22 +1205,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:49</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:49</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1241,43 +1241,43 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134665030</t>
+          <t>https://artportalen.se/Sighting/136042876</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134665031</v>
+        <v>136042877</v>
       </c>
       <c r="B7" t="n">
-        <v>99195</v>
+        <v>93361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1286,13 +1286,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>802233</v>
+        <v>802522</v>
       </c>
       <c r="R7" t="n">
-        <v>7353488</v>
+        <v>7353174</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1316,22 +1316,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1362,43 +1352,43 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134665031</t>
+          <t>https://artportalen.se/Sighting/136042877</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134850251</v>
+        <v>134664983</v>
       </c>
       <c r="B8" t="n">
-        <v>99195</v>
+        <v>91995</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1407,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>802268</v>
+        <v>802121</v>
       </c>
       <c r="R8" t="n">
-        <v>7353487</v>
+        <v>7353580</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1437,22 +1427,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1483,43 +1473,43 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134850251</t>
+          <t>https://artportalen.se/Sighting/134664983</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134850252</v>
+        <v>135058972</v>
       </c>
       <c r="B9" t="n">
-        <v>99195</v>
+        <v>92064</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1528,13 +1518,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>802319</v>
+        <v>802158</v>
       </c>
       <c r="R9" t="n">
-        <v>7353445</v>
+        <v>7353566</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1558,22 +1548,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:13</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:13</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1604,13 +1584,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134850252</t>
+          <t>https://artportalen.se/Sighting/135058972</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134850253</v>
+        <v>134665030</v>
       </c>
       <c r="B10" t="n">
         <v>99195</v>
@@ -1640,7 +1620,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1649,10 +1629,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>802261</v>
+        <v>802203</v>
       </c>
       <c r="R10" t="n">
-        <v>7353494</v>
+        <v>7353559</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1679,22 +1659,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1725,16 +1705,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134850253</t>
+          <t>https://artportalen.se/Sighting/134665030</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135058973</v>
+        <v>134665031</v>
       </c>
       <c r="B11" t="n">
-        <v>99269</v>
+        <v>99195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1761,7 +1741,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1770,13 +1750,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>802216</v>
+        <v>802233</v>
       </c>
       <c r="R11" t="n">
-        <v>7353485</v>
+        <v>7353488</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1803,9 +1783,19 @@
           <t>2026-06-23</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1836,16 +1826,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135058973</t>
+          <t>https://artportalen.se/Sighting/134665031</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135058974</v>
+        <v>134850251</v>
       </c>
       <c r="B12" t="n">
-        <v>99269</v>
+        <v>99195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,7 +1862,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1881,13 +1871,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>802205</v>
+        <v>802268</v>
       </c>
       <c r="R12" t="n">
-        <v>7353479</v>
+        <v>7353487</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1911,12 +1901,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1947,43 +1947,43 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135058974</t>
+          <t>https://artportalen.se/Sighting/134850251</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134665048</v>
+        <v>134850252</v>
       </c>
       <c r="B13" t="n">
-        <v>106324</v>
+        <v>99195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>802272</v>
+        <v>802319</v>
       </c>
       <c r="R13" t="n">
-        <v>7353376</v>
+        <v>7353445</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2022,22 +2022,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2068,43 +2068,43 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134665048</t>
+          <t>https://artportalen.se/Sighting/134850252</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135058971</v>
+        <v>134850253</v>
       </c>
       <c r="B14" t="n">
-        <v>106406</v>
+        <v>99195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2113,13 +2113,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>802177</v>
+        <v>802261</v>
       </c>
       <c r="R14" t="n">
-        <v>7353299</v>
+        <v>7353494</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2143,12 +2143,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2179,43 +2189,43 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135058971</t>
+          <t>https://artportalen.se/Sighting/134850253</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135058975</v>
+        <v>135058973</v>
       </c>
       <c r="B15" t="n">
-        <v>106406</v>
+        <v>99269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2224,10 +2234,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>802278</v>
+        <v>802216</v>
       </c>
       <c r="R15" t="n">
-        <v>7353385</v>
+        <v>7353485</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2290,7 +2300,824 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135058973</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135058974</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>802205</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7353479</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135058974</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136042757</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99292</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>802380</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7353175</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136042757</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134665048</v>
+      </c>
+      <c r="B18" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>802272</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7353376</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665048</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135058971</v>
+      </c>
+      <c r="B19" t="n">
+        <v>106406</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>802177</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7353299</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135058971</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135058975</v>
+      </c>
+      <c r="B20" t="n">
+        <v>106406</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>802278</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7353385</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135058975</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136042763</v>
+      </c>
+      <c r="B21" t="n">
+        <v>106432</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>802366</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7353167</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136042763</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136042764</v>
+      </c>
+      <c r="B22" t="n">
+        <v>106432</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>802378</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7353172</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136042764</t>
         </is>
       </c>
     </row>
@@ -2310,6 +3137,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30513-2026 artfynd.xlsx
+++ b/artfynd/A 30513-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>136042742</v>
       </c>
       <c r="B4" t="n">
-        <v>93353</v>
+        <v>93354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136042770</v>
       </c>
       <c r="B5" t="n">
-        <v>93361</v>
+        <v>93362</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136042876</v>
       </c>
       <c r="B6" t="n">
-        <v>93361</v>
+        <v>93362</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136042877</v>
       </c>
       <c r="B7" t="n">
-        <v>93361</v>
+        <v>93362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>136042757</v>
       </c>
       <c r="B17" t="n">
-        <v>99292</v>
+        <v>99293</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136042763</v>
       </c>
       <c r="B21" t="n">
-        <v>106432</v>
+        <v>106433</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136042764</v>
       </c>
       <c r="B22" t="n">
-        <v>106432</v>
+        <v>106433</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 30513-2026 artfynd.xlsx
+++ b/artfynd/A 30513-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>136042742</v>
       </c>
       <c r="B4" t="n">
-        <v>93354</v>
+        <v>93355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136042770</v>
       </c>
       <c r="B5" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136042876</v>
       </c>
       <c r="B6" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136042877</v>
       </c>
       <c r="B7" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>136042757</v>
       </c>
       <c r="B17" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136042763</v>
       </c>
       <c r="B21" t="n">
-        <v>106433</v>
+        <v>106435</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136042764</v>
       </c>
       <c r="B22" t="n">
-        <v>106433</v>
+        <v>106435</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 30513-2026 artfynd.xlsx
+++ b/artfynd/A 30513-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>136042742</v>
       </c>
       <c r="B4" t="n">
-        <v>93355</v>
+        <v>93356</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136042770</v>
       </c>
       <c r="B5" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136042876</v>
       </c>
       <c r="B6" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136042877</v>
       </c>
       <c r="B7" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>136042757</v>
       </c>
       <c r="B17" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136042763</v>
       </c>
       <c r="B21" t="n">
-        <v>106435</v>
+        <v>106436</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136042764</v>
       </c>
       <c r="B22" t="n">
-        <v>106435</v>
+        <v>106436</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 30513-2026 artfynd.xlsx
+++ b/artfynd/A 30513-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>136042742</v>
       </c>
       <c r="B4" t="n">
-        <v>93356</v>
+        <v>93357</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136042770</v>
       </c>
       <c r="B5" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136042876</v>
       </c>
       <c r="B6" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136042877</v>
       </c>
       <c r="B7" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>136042757</v>
       </c>
       <c r="B17" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136042763</v>
       </c>
       <c r="B21" t="n">
-        <v>106436</v>
+        <v>106437</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136042764</v>
       </c>
       <c r="B22" t="n">
-        <v>106436</v>
+        <v>106437</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 30513-2026 artfynd.xlsx
+++ b/artfynd/A 30513-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>136042742</v>
       </c>
       <c r="B4" t="n">
-        <v>93357</v>
+        <v>93363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136042770</v>
       </c>
       <c r="B5" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136042876</v>
       </c>
       <c r="B6" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136042877</v>
       </c>
       <c r="B7" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>136042757</v>
       </c>
       <c r="B17" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136042763</v>
       </c>
       <c r="B21" t="n">
-        <v>106437</v>
+        <v>106443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136042764</v>
       </c>
       <c r="B22" t="n">
-        <v>106437</v>
+        <v>106443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 30513-2026 artfynd.xlsx
+++ b/artfynd/A 30513-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>136042742</v>
       </c>
       <c r="B4" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136042770</v>
       </c>
       <c r="B5" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136042876</v>
       </c>
       <c r="B6" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136042877</v>
       </c>
       <c r="B7" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>136042757</v>
       </c>
       <c r="B17" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136042763</v>
       </c>
       <c r="B21" t="n">
-        <v>106443</v>
+        <v>106444</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136042764</v>
       </c>
       <c r="B22" t="n">
-        <v>106443</v>
+        <v>106444</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 30513-2026 artfynd.xlsx
+++ b/artfynd/A 30513-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>136042742</v>
       </c>
       <c r="B4" t="n">
-        <v>93364</v>
+        <v>93370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136042770</v>
       </c>
       <c r="B5" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136042876</v>
       </c>
       <c r="B6" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136042877</v>
       </c>
       <c r="B7" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>136042757</v>
       </c>
       <c r="B17" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136042763</v>
       </c>
       <c r="B21" t="n">
-        <v>106444</v>
+        <v>106455</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136042764</v>
       </c>
       <c r="B22" t="n">
-        <v>106444</v>
+        <v>106455</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 30513-2026 artfynd.xlsx
+++ b/artfynd/A 30513-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>136042742</v>
       </c>
       <c r="B4" t="n">
-        <v>93370</v>
+        <v>93377</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136042770</v>
       </c>
       <c r="B5" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136042876</v>
       </c>
       <c r="B6" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136042877</v>
       </c>
       <c r="B7" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>136042757</v>
       </c>
       <c r="B17" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136042763</v>
       </c>
       <c r="B21" t="n">
-        <v>106455</v>
+        <v>106468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136042764</v>
       </c>
       <c r="B22" t="n">
-        <v>106455</v>
+        <v>106468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 30513-2026 artfynd.xlsx
+++ b/artfynd/A 30513-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>136042742</v>
       </c>
       <c r="B4" t="n">
-        <v>93377</v>
+        <v>93378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136042770</v>
       </c>
       <c r="B5" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136042876</v>
       </c>
       <c r="B6" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136042877</v>
       </c>
       <c r="B7" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>136042757</v>
       </c>
       <c r="B17" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136042763</v>
       </c>
       <c r="B21" t="n">
-        <v>106468</v>
+        <v>106469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136042764</v>
       </c>
       <c r="B22" t="n">
-        <v>106468</v>
+        <v>106469</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 30513-2026 artfynd.xlsx
+++ b/artfynd/A 30513-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>136042742</v>
       </c>
       <c r="B4" t="n">
-        <v>93378</v>
+        <v>93391</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136042770</v>
       </c>
       <c r="B5" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136042876</v>
       </c>
       <c r="B6" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136042877</v>
       </c>
       <c r="B7" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>136042757</v>
       </c>
       <c r="B17" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136042763</v>
       </c>
       <c r="B21" t="n">
-        <v>106469</v>
+        <v>106482</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136042764</v>
       </c>
       <c r="B22" t="n">
-        <v>106469</v>
+        <v>106482</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 30513-2026 artfynd.xlsx
+++ b/artfynd/A 30513-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>136042742</v>
       </c>
       <c r="B4" t="n">
-        <v>93391</v>
+        <v>93392</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136042770</v>
       </c>
       <c r="B5" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136042876</v>
       </c>
       <c r="B6" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136042877</v>
       </c>
       <c r="B7" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>136042757</v>
       </c>
       <c r="B17" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136042763</v>
       </c>
       <c r="B21" t="n">
-        <v>106482</v>
+        <v>106483</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136042764</v>
       </c>
       <c r="B22" t="n">
-        <v>106482</v>
+        <v>106483</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
